--- a/output/pdf_financials_xlsx/WLF.xlsx
+++ b/output/pdf_financials_xlsx/WLF.xlsx
@@ -7845,7 +7845,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
